--- a/港岛-湾仔-活道1号/活道1号_销控明细表.xlsx
+++ b/港岛-湾仔-活道1号/活道1号_销控明细表.xlsx
@@ -2754,7 +2754,7 @@
           <t>A | 940呎 (3房)
 $2800万
 $29,786/呎
-(26年-06月)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
@@ -2762,7 +2762,7 @@
           <t>B | 949呎 (3房)
 $2550万
 $26,870/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
     </row>
@@ -2777,7 +2777,7 @@
           <t>A | 461呎 (2房)
 $1100万
 $23,855/呎
-(25年-09月)</t>
+(25年-09月-22日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -2785,7 +2785,7 @@
           <t>B | 461呎 (2房)
 $1060万
 $22,993/呎
-(25年-09月)</t>
+(25年-09月-25日)</t>
         </is>
       </c>
     </row>
@@ -2800,7 +2800,7 @@
           <t>A | 461呎 (2房)
 $1080万
 $23,416/呎
-(25年-09月)</t>
+(25年-09月-16日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -2808,7 +2808,7 @@
           <t>B | 461呎 (2房)
 $1039万
 $22,534/呎
-(25年-09月)</t>
+(25年-09月-11日)</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
           <t>A | 461呎 (2房)
 $1058万
 $22,959/呎
-(25年-09月)</t>
+(25年-09月-11日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -2831,7 +2831,7 @@
           <t>B | 461呎 (2房)
 $1018万
 $22,089/呎
-(25年-09月)</t>
+(25年-09月-11日)</t>
         </is>
       </c>
     </row>
@@ -2846,7 +2846,7 @@
           <t>A | 461呎 (2房)
 $1038万
 $22,508/呎
-(25年-09月)</t>
+(25年-09月-22日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -2854,7 +2854,7 @@
           <t>B | 461呎 (2房)
 $998万
 $21,655/呎
-(25年-09月)</t>
+(25年-09月-17日)</t>
         </is>
       </c>
     </row>
@@ -2869,7 +2869,7 @@
           <t>A | 461呎 (2房)
 $1017万
 $22,067/呎
-(25年-09月)</t>
+(25年-09月-18日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -2877,7 +2877,7 @@
           <t>B | 461呎 (2房)
 $979万
 $21,232/呎
-(25年-09月)</t>
+(25年-09月-21日)</t>
         </is>
       </c>
     </row>
@@ -2892,7 +2892,7 @@
           <t>A | 461呎 (2房)
 $997万
 $21,633/呎
-(25年-09月)</t>
+(25年-09月-08日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -2900,7 +2900,7 @@
           <t>B | 461呎 (2房)
 $960万
 $20,816/呎
-(25年-09月)</t>
+(25年-09月-14日)</t>
         </is>
       </c>
     </row>
@@ -2915,7 +2915,7 @@
           <t>A | 461呎 (2房)
 $978万
 $21,210/呎
-(25年-09月)</t>
+(25年-09月-17日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -2923,7 +2923,7 @@
           <t>B | 461呎 (2房)
 $941万
 $20,408/呎
-(25年-09月)</t>
+(25年-09月-10日)</t>
         </is>
       </c>
     </row>
@@ -2938,7 +2938,7 @@
           <t>A | 461呎 (2房)
 $1282万
 $27,809/呎
-(24年-10月)</t>
+(24年-10月-20日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -2946,7 +2946,7 @@
           <t>B | 461呎 (2房)
 $925万
 $20,074/呎
-(25年-09月)</t>
+(25年-09月-10日)</t>
         </is>
       </c>
     </row>
@@ -2961,7 +2961,7 @@
           <t>A | 461呎 (2房)
 $945万
 $20,503/呎
-(25年-09月)</t>
+(25年-09月-04日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -2969,7 +2969,7 @@
           <t>B | 461呎 (2房)
 $910万
 $19,740/呎
-(25年-09月)</t>
+(25年-09月-22日)</t>
         </is>
       </c>
     </row>
@@ -2984,7 +2984,7 @@
           <t>A | 461呎 (2房)
 $1231万
 $26,707/呎
-(25年-05月)</t>
+(25年-05月-13日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -2992,7 +2992,7 @@
           <t>B | 461呎 (2房)
 $901万
 $19,553/呎
-(25年-09月)</t>
+(25年-09月-22日)</t>
         </is>
       </c>
     </row>
@@ -3007,7 +3007,7 @@
           <t>A | 461呎 (2房)
 $966万
 $20,961/呎
-(25年-09月)</t>
+(25年-09月-15日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -3015,7 +3015,7 @@
           <t>B | 461呎 (2房)
 $932万
 $20,208/呎
-(25年-09月)</t>
+(25年-09月-14日)</t>
         </is>
       </c>
     </row>
@@ -3030,7 +3030,7 @@
           <t>A | 461呎 (2房)
 $926万
 $20,098/呎
-(25年-09月)</t>
+(25年-09月-16日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -3038,7 +3038,7 @@
           <t>B | 461呎 (2房)
 $894万
 $19,388/呎
-(25年-09月)</t>
+(25年-09月-25日)</t>
         </is>
       </c>
     </row>
@@ -3053,7 +3053,7 @@
           <t>A | 461呎 (2房)
 $911万
 $19,770/呎
-(25年-09月)</t>
+(25年-09月-21日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -3061,7 +3061,7 @@
           <t>B | 461呎 (2房)
 $885万
 $19,206/呎
-(25年-09月)</t>
+(25年-09月-08日)</t>
         </is>
       </c>
     </row>
@@ -3076,7 +3076,7 @@
           <t>A | 461呎 (2房)
 $1160万
 $25,174/呎
-(24年-12月)</t>
+(24年-12月-16日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -3084,7 +3084,7 @@
           <t>B | 461呎 (2房)
 $874万
 $18,952/呎
-(25年-09月)</t>
+(25年-09月-10日)</t>
         </is>
       </c>
     </row>
@@ -3099,7 +3099,7 @@
           <t>A | 461呎 (2房)
 $876万
 $19,000/呎
-(25年-09月)</t>
+(25年-09月-11日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -3107,7 +3107,7 @@
           <t>B | 461呎 (2房)
 $1112万
 $24,132/呎
-(25年-07月)</t>
+(25年-07月-02日)</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
           <t>A | 461呎 (2房)
 $859万
 $18,631/呎
-(25年-09月)</t>
+(25年-09月-09日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -3130,7 +3130,7 @@
           <t>B | 461呎 (2房)
 $1091万
 $23,657/呎
-(25年-06月)</t>
+(25年-06月-29日)</t>
         </is>
       </c>
     </row>
@@ -3145,7 +3145,7 @@
           <t>A | 461呎 (2房)
 $848万
 $18,397/呎
-(25年-09月)</t>
+(25年-09月-24日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -3153,7 +3153,7 @@
           <t>B | 461呎 (2房)
 $1077万
 $23,364/呎
-(24年-11月)</t>
+(24年-11月-24日)</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3168,7 @@
           <t>A | 461呎 (2房)
 $837万
 $18,148/呎
-(25年-09月)</t>
+(25年-09月-08日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -3176,7 +3176,7 @@
           <t>B | 461呎 (2房)
 $1063万
 $23,067/呎
-(24年-11月)</t>
+(24年-11月-24日)</t>
         </is>
       </c>
     </row>
@@ -3191,7 +3191,7 @@
           <t>A | 461呎 (2房)
 $868万
 $18,831/呎
-(25年-09月)</t>
+(25年-09月-25日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -3199,7 +3199,7 @@
           <t>B | 461呎 (2房)
 $860万
 $18,655/呎
-(25年-09月)</t>
+(25年-09月-25日)</t>
         </is>
       </c>
     </row>
@@ -3222,7 +3222,7 @@
           <t>B | 1279呎 (3房)
 $2880万
 $22,516/呎
-(26年-01月)</t>
+(26年-01月-26日)</t>
         </is>
       </c>
     </row>

--- a/港岛-湾仔-活道1号/活道1号_销控明细表.xlsx
+++ b/港岛-湾仔-活道1号/活道1号_销控明细表.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -119,12 +119,6 @@
       <color rgb="00660000"/>
       <sz val="8"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="8"/>
-    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -196,7 +190,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -256,9 +250,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2612,19 +2603,19 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
-        <v>35080000</v>
+        <v>29818000</v>
       </c>
       <c r="I44" s="5" t="n">
-        <v>27321</v>
+        <v>23223</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
@@ -2702,7 +2693,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -2712,7 +2703,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>42</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -3209,12 +3200,12 @@
           <t>2&amp;3</t>
         </is>
       </c>
-      <c r="B25" s="21" t="inlineStr">
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>A | 1284呎 (3房)
-$3508万
-$27,321/呎
-(在售)</t>
+$2982万
+$23,223/呎
+(26年-08月-25日)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
